--- a/data/trans_camb/P57GLOBAL_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P57GLOBAL_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 4,24</t>
+          <t>-9,45; 4,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 9,6</t>
+          <t>-3,09; 9,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-36,47; -19,25</t>
+          <t>-36,43; -19,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 0,43</t>
+          <t>-10,73; 0,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 0,85</t>
+          <t>-11,24; -0,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-37,08; -24,85</t>
+          <t>-36,33; -24,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 0,85</t>
+          <t>-7,89; 0,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 3,05</t>
+          <t>-5,06; 3,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-34,46; -24,26</t>
+          <t>-34,25; -24,02</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 5,51</t>
+          <t>-11,21; 6,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 12,09</t>
+          <t>-3,61; 12,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-43,97; -24,26</t>
+          <t>-43,52; -24,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 0,48</t>
+          <t>-11,62; 0,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 0,94</t>
+          <t>-12,06; -0,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,11; -28,11</t>
+          <t>-39,39; -27,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 0,99</t>
+          <t>-9,04; 0,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 3,57</t>
+          <t>-5,82; 3,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-39,4; -28,5</t>
+          <t>-39,35; -28,39</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 0,15</t>
+          <t>-12,35; 0,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,49; 26,04</t>
+          <t>14,51; 25,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 7,75</t>
+          <t>-7,22; 7,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,35; -4,51</t>
+          <t>-16,58; -4,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,43; 18,59</t>
+          <t>8,15; 18,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,67; -6,34</t>
+          <t>-17,68; -6,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,1; -4,05</t>
+          <t>-13,3; -4,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,3; 21,36</t>
+          <t>12,84; 20,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,22; -1,41</t>
+          <t>-10,19; -1,12</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 0,26</t>
+          <t>-18,77; 0,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,86; 45,24</t>
+          <t>22,38; 44,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 12,84</t>
+          <t>-10,99; 11,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,86; -6,83</t>
+          <t>-22,94; -6,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,5; 28,08</t>
+          <t>11,26; 27,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,6; -9,82</t>
+          <t>-24,63; -9,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,29; -6,35</t>
+          <t>-19,63; -6,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,41; 33,4</t>
+          <t>18,87; 32,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-15,05; -2,28</t>
+          <t>-15,0; -1,74</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 9,13</t>
+          <t>-5,05; 9,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,69; 21,89</t>
+          <t>7,3; 21,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,96; -7,66</t>
+          <t>-23,95; -7,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,25; 24,85</t>
+          <t>11,08; 25,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,76; 31,23</t>
+          <t>18,1; 30,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 3,3</t>
+          <t>-10,89; 3,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,64; 14,8</t>
+          <t>4,85; 15,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,49; 23,89</t>
+          <t>15,12; 24,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,56; -3,75</t>
+          <t>-14,37; -4,09</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 15,17</t>
+          <t>-7,57; 15,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,39; 36,66</t>
+          <t>10,72; 36,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,31; -13,19</t>
+          <t>-35,65; -13,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,53; 46,25</t>
+          <t>17,49; 47,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,13; 57,9</t>
+          <t>29,34; 56,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 6,01</t>
+          <t>-17,45; 6,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,38; 25,46</t>
+          <t>7,58; 26,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22,35; 41,15</t>
+          <t>23,13; 42,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-23,2; -6,47</t>
+          <t>-22,47; -6,87</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-25,61; -11,3</t>
+          <t>-24,93; -10,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-31,67; -17,81</t>
+          <t>-31,45; -17,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-46,11; -29,83</t>
+          <t>-46,35; -30,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,37; -0,74</t>
+          <t>-14,69; -1,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-19,78; -5,5</t>
+          <t>-19,46; -5,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-55,95; -33,24</t>
+          <t>-55,28; -33,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-17,77; -8,27</t>
+          <t>-18,32; -8,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-24,06; -14,27</t>
+          <t>-23,94; -14,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-49,64; -34,52</t>
+          <t>-50,49; -35,04</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-34,4; -16,45</t>
+          <t>-33,21; -14,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,95; -25,72</t>
+          <t>-42,21; -25,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-62,59; -43,02</t>
+          <t>-62,26; -43,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-19,49; -1,17</t>
+          <t>-20,08; -2,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,46; -7,85</t>
+          <t>-26,68; -8,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-75,54; -47,29</t>
+          <t>-75,09; -47,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-24,04; -11,99</t>
+          <t>-24,44; -11,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,58; -20,1</t>
+          <t>-31,98; -19,88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-69,47; -49,15</t>
+          <t>-68,84; -49,08</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-32,3; -13,65</t>
+          <t>-31,41; -13,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,76; 18,03</t>
+          <t>3,54; 16,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,54; 19,25</t>
+          <t>5,57; 18,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-19,9; -4,6</t>
+          <t>-19,99; -3,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 11,66</t>
+          <t>0,02; 11,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,89; 11,64</t>
+          <t>0,39; 11,45</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-23,64; -11,1</t>
+          <t>-23,19; -11,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,17; 12,12</t>
+          <t>2,49; 11,61</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,23; 12,96</t>
+          <t>4,7; 13,23</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-38,02; -17,68</t>
+          <t>-37,89; -17,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4,41; 24,21</t>
+          <t>4,32; 22,67</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6,69; 25,49</t>
+          <t>6,63; 24,97</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-22,52; -5,64</t>
+          <t>-22,32; -4,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 14,38</t>
+          <t>0,04; 13,97</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,0; 14,16</t>
+          <t>0,43; 13,78</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-27,54; -13,55</t>
+          <t>-27,01; -14,24</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3,63; 15,06</t>
+          <t>3,06; 14,37</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4,99; 16,23</t>
+          <t>5,4; 16,54</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 1,8</t>
+          <t>-13,73; 1,96</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,6; 15,48</t>
+          <t>0,53; 15,43</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-38,88; -23,19</t>
+          <t>-38,87; -23,45</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 11,51</t>
+          <t>-2,78; 11,6</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,13; 15,71</t>
+          <t>1,12; 14,85</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-39,35; -25,85</t>
+          <t>-39,33; -25,31</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 4,56</t>
+          <t>-6,58; 4,59</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3,31; 13,22</t>
+          <t>2,57; 12,96</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-36,76; -26,3</t>
+          <t>-37,01; -26,4</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-18,69; 2,78</t>
+          <t>-18,59; 3,12</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0,79; 23,09</t>
+          <t>0,78; 23,19</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-51,03; -34,25</t>
+          <t>-51,43; -34,28</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 16,59</t>
+          <t>-3,54; 16,7</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,48; 22,59</t>
+          <t>1,36; 21,14</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-50,91; -36,78</t>
+          <t>-51,13; -35,72</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 6,46</t>
+          <t>-8,72; 6,52</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4,41; 19,16</t>
+          <t>3,44; 18,61</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-49,26; -37,53</t>
+          <t>-49,7; -37,32</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,04; 13,67</t>
+          <t>2,17; 13,4</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>26,05; 36,48</t>
+          <t>26,18; 36,44</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5,97; 18,43</t>
+          <t>5,61; 17,57</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16,18; 26,78</t>
+          <t>15,81; 26,45</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>33,36; 42,67</t>
+          <t>33,66; 43,07</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,48; 21,14</t>
+          <t>10,45; 21,58</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,01; 18,83</t>
+          <t>11,33; 19,21</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>31,4; 38,34</t>
+          <t>31,32; 38,19</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9,89; 18,02</t>
+          <t>9,49; 17,89</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>3,59; 27,26</t>
+          <t>3,81; 26,13</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>45,54; 72,88</t>
+          <t>45,81; 71,99</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10,56; 36,57</t>
+          <t>10,12; 34,66</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>30,37; 57,11</t>
+          <t>29,59; 56,16</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>62,15; 91,92</t>
+          <t>63,07; 92,17</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,89; 45,23</t>
+          <t>19,51; 46,52</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,28; 37,9</t>
+          <t>20,8; 38,37</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>57,74; 77,84</t>
+          <t>57,32; 77,22</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>18,05; 36,17</t>
+          <t>17,4; 35,77</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>4,71; 11,47</t>
+          <t>4,63; 11,37</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>6,68; 13,28</t>
+          <t>6,78; 13,31</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-56,32; 3,36</t>
+          <t>-53,64; 3,62</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 5,01</t>
+          <t>-1,39; 4,76</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>4,23; 9,57</t>
+          <t>3,72; 9,08</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 3,08</t>
+          <t>-3,37; 3,13</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,03</t>
+          <t>2,39; 7,16</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>6,14; 10,32</t>
+          <t>6,09; 10,44</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-40,44; 1,79</t>
+          <t>-43,6; 1,82</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>5,58; 14,32</t>
+          <t>5,47; 14,07</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>7,84; 16,51</t>
+          <t>8,0; 16,44</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-67,03; 4,0</t>
+          <t>-64,46; 4,33</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 5,76</t>
+          <t>-1,55; 5,48</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>4,71; 11,17</t>
+          <t>4,08; 10,47</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 3,61</t>
+          <t>-3,77; 3,62</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,6; 8,27</t>
+          <t>2,73; 8,52</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>7,01; 12,21</t>
+          <t>6,98; 12,44</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-46,57; 2,11</t>
+          <t>-51,25; 2,1</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,68</t>
+          <t>-3,95; 0,71</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>9,39; 13,82</t>
+          <t>9,49; 13,74</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-25,26; -6,42</t>
+          <t>-26,27; -6,62</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,2</t>
+          <t>1,11; 5,15</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>10,43; 14,45</t>
+          <t>10,49; 14,48</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-13,74; -6,81</t>
+          <t>-14,6; -7,22</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,31</t>
+          <t>-0,85; 2,35</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>10,6; 13,41</t>
+          <t>10,54; 13,35</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-19,1; -7,57</t>
+          <t>-19,12; -7,77</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 0,98</t>
+          <t>-5,51; 1,04</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>13,08; 20,09</t>
+          <t>13,19; 19,84</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-35,96; -9,21</t>
+          <t>-37,49; -9,43</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1,34; 7,32</t>
+          <t>1,5; 7,2</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>14,24; 20,41</t>
+          <t>14,2; 20,41</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-18,93; -9,53</t>
+          <t>-20,15; -10,19</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 3,28</t>
+          <t>-1,16; 3,3</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>14,65; 18,99</t>
+          <t>14,59; 18,99</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-26,82; -10,67</t>
+          <t>-26,85; -10,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57GLOBAL_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P57GLOBAL_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-28,28</t>
+          <t>-25,53</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-30,74</t>
+          <t>-30,06</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-29,53</t>
+          <t>-27,71</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 4,83</t>
+          <t>-9,85; 4,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 9,45</t>
+          <t>-3,54; 8,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-36,43; -19,8</t>
+          <t>-33,02; -17,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 0,42</t>
+          <t>-10,27; 0,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,24; -0,16</t>
+          <t>-10,59; 0,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,33; -24,65</t>
+          <t>-35,63; -23,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 0,79</t>
+          <t>-7,86; 0,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 3,16</t>
+          <t>-5,23; 3,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-34,25; -24,02</t>
+          <t>-32,71; -22,7</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-34,65%</t>
+          <t>-31,27%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-33,77%</t>
+          <t>-33,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-34,25%</t>
+          <t>-32,13%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 6,14</t>
+          <t>-11,67; 5,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 12,04</t>
+          <t>-4,13; 11,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-43,52; -24,8</t>
+          <t>-39,45; -22,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 0,46</t>
+          <t>-11,03; 0,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,06; -0,16</t>
+          <t>-11,58; 0,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,39; -27,78</t>
+          <t>-38,6; -27,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 0,94</t>
+          <t>-8,96; 0,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 3,78</t>
+          <t>-5,96; 3,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-39,35; -28,39</t>
+          <t>-37,2; -27,08</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-11,76</t>
+          <t>-11,47</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-5,64</t>
+          <t>-5,4</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 0,56</t>
+          <t>-13,66; -0,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,51; 25,99</t>
+          <t>14,63; 26,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 7,12</t>
+          <t>-6,74; 7,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,58; -4,67</t>
+          <t>-17,25; -4,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,15; 18,31</t>
+          <t>8,24; 19,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,68; -6,33</t>
+          <t>-16,5; -5,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,3; -4,18</t>
+          <t>-13,51; -4,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,84; 20,52</t>
+          <t>12,98; 21,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,19; -1,12</t>
+          <t>-10,06; -1,11</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-16,93%</t>
+          <t>-16,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-8,53%</t>
+          <t>-8,15%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,77; 0,79</t>
+          <t>-20,75; -0,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,38; 44,74</t>
+          <t>22,21; 44,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 11,72</t>
+          <t>-10,2; 12,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,94; -6,85</t>
+          <t>-24,07; -6,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,26; 27,41</t>
+          <t>11,5; 29,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,63; -9,44</t>
+          <t>-23,49; -8,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,63; -6,64</t>
+          <t>-19,54; -6,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,87; 32,43</t>
+          <t>19,07; 33,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-15,0; -1,74</t>
+          <t>-14,8; -1,78</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-15,75</t>
+          <t>-15,09</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,35</t>
+          <t>-2,38</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-9,37</t>
+          <t>-8,51</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 9,41</t>
+          <t>-5,85; 9,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,3; 21,46</t>
+          <t>7,11; 21,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-23,95; -7,93</t>
+          <t>-22,57; -6,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,08; 25,14</t>
+          <t>11,22; 25,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,1; 30,74</t>
+          <t>18,06; 31,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 3,82</t>
+          <t>-8,94; 5,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,85; 15,47</t>
+          <t>5,05; 15,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,12; 24,42</t>
+          <t>14,7; 24,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,37; -4,09</t>
+          <t>-13,57; -3,0</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-24,53%</t>
+          <t>-23,5%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-5,74%</t>
+          <t>-4,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-15,31%</t>
+          <t>-13,9%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 15,47</t>
+          <t>-8,53; 15,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,72; 36,43</t>
+          <t>10,33; 35,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,65; -13,31</t>
+          <t>-33,22; -11,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,49; 47,26</t>
+          <t>18,0; 47,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,34; 56,94</t>
+          <t>29,52; 60,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,45; 6,92</t>
+          <t>-14,52; 10,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,58; 26,85</t>
+          <t>7,92; 26,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,13; 42,28</t>
+          <t>23,1; 42,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-22,47; -6,87</t>
+          <t>-21,38; -5,2</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-38,67</t>
+          <t>-37,92</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-42,23</t>
+          <t>-33,72</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-40,92</t>
+          <t>-35,73</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-24,93; -10,23</t>
+          <t>-25,72; -11,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-31,45; -17,68</t>
+          <t>-31,45; -17,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-46,35; -30,69</t>
+          <t>-45,95; -30,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,69; -1,38</t>
+          <t>-14,61; -1,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-19,46; -5,86</t>
+          <t>-19,29; -5,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-55,28; -33,25</t>
+          <t>-39,91; -26,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-18,32; -8,39</t>
+          <t>-18,23; -8,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-23,94; -14,09</t>
+          <t>-23,63; -13,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-50,49; -35,04</t>
+          <t>-41,08; -30,41</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-53,35%</t>
+          <t>-52,32%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-59,27%</t>
+          <t>-47,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-56,95%</t>
+          <t>-49,72%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,21; -14,9</t>
+          <t>-34,32; -16,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-42,21; -25,3</t>
+          <t>-42,31; -24,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-62,26; -43,25</t>
+          <t>-61,16; -42,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,08; -2,08</t>
+          <t>-19,47; -2,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,68; -8,84</t>
+          <t>-26,2; -8,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-75,09; -47,76</t>
+          <t>-54,21; -39,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-24,44; -11,97</t>
+          <t>-24,68; -11,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-31,98; -19,88</t>
+          <t>-31,9; -19,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-68,84; -49,08</t>
+          <t>-55,66; -43,23</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11,8</t>
+          <t>11,11</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,82</t>
+          <t>6,25</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8,76</t>
+          <t>8,67</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-31,41; -13,58</t>
+          <t>-31,92; -14,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,54; 16,86</t>
+          <t>3,54; 17,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,57; 18,68</t>
+          <t>4,09; 18,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-19,99; -3,79</t>
+          <t>-19,62; -4,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,02; 11,55</t>
+          <t>-0,82; 11,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,39; 11,45</t>
+          <t>1,44; 11,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-23,19; -11,62</t>
+          <t>-23,49; -11,99</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,49; 11,61</t>
+          <t>3,02; 12,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,7; 13,23</t>
+          <t>4,65; 13,11</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-37,89; -17,79</t>
+          <t>-38,56; -18,64</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4,32; 22,67</t>
+          <t>4,31; 22,79</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6,63; 24,97</t>
+          <t>5,09; 23,65</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-22,32; -4,51</t>
+          <t>-22,27; -6,3</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,04; 13,97</t>
+          <t>-0,78; 13,75</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,43; 13,78</t>
+          <t>1,29; 14,67</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-27,01; -14,24</t>
+          <t>-27,49; -14,68</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3,06; 14,37</t>
+          <t>3,47; 14,83</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5,4; 16,54</t>
+          <t>5,41; 16,24</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-31,02</t>
+          <t>-28,9</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-32,6</t>
+          <t>-31,42</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-31,83</t>
+          <t>-30,17</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 1,96</t>
+          <t>-14,14; 1,49</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,53; 15,43</t>
+          <t>1,03; 15,37</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-38,87; -23,45</t>
+          <t>-35,97; -20,95</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 11,6</t>
+          <t>-3,03; 11,41</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,12; 14,85</t>
+          <t>0,51; 14,59</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-39,33; -25,31</t>
+          <t>-38,43; -24,52</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 4,59</t>
+          <t>-6,09; 4,74</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2,57; 12,96</t>
+          <t>2,93; 13,15</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-37,01; -26,4</t>
+          <t>-34,93; -24,72</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-43,34%</t>
+          <t>-40,38%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-44,3%</t>
+          <t>-42,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-43,84%</t>
+          <t>-41,56%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-18,59; 3,12</t>
+          <t>-19,3; 2,21</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0,78; 23,19</t>
+          <t>1,38; 22,92</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-51,43; -34,28</t>
+          <t>-48,46; -31,18</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 16,7</t>
+          <t>-3,97; 16,47</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,36; 21,14</t>
+          <t>0,73; 20,9</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-51,13; -35,72</t>
+          <t>-49,77; -35,23</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 6,52</t>
+          <t>-8,11; 6,88</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3,44; 18,61</t>
+          <t>3,98; 19,04</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-49,7; -37,32</t>
+          <t>-47,04; -35,67</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11,53</t>
+          <t>12,43</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,9</t>
+          <t>16,46</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>13,75</t>
+          <t>14,48</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,17; 13,4</t>
+          <t>1,89; 13,44</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>26,18; 36,44</t>
+          <t>26,14; 35,94</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5,61; 17,57</t>
+          <t>6,58; 18,39</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15,81; 26,45</t>
+          <t>16,09; 27,47</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>33,66; 43,07</t>
+          <t>33,98; 43,65</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,45; 21,58</t>
+          <t>11,94; 21,5</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,33; 19,21</t>
+          <t>11,11; 18,46</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>31,32; 38,19</t>
+          <t>31,78; 38,54</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9,49; 17,89</t>
+          <t>10,76; 18,49</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>3,81; 26,13</t>
+          <t>3,27; 26,45</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>45,81; 71,99</t>
+          <t>45,73; 71,49</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10,12; 34,66</t>
+          <t>11,66; 35,9</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>29,59; 56,16</t>
+          <t>30,76; 59,29</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>63,07; 92,17</t>
+          <t>63,94; 94,79</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,51; 46,52</t>
+          <t>22,79; 46,57</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,8; 38,37</t>
+          <t>21,07; 37,57</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>57,32; 77,22</t>
+          <t>58,63; 78,33</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>17,4; 35,77</t>
+          <t>19,99; 37,14</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-20,32</t>
+          <t>2,44</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,3</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-11,94</t>
+          <t>1,03</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>4,63; 11,37</t>
+          <t>4,54; 11,3</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>6,78; 13,31</t>
+          <t>6,67; 12,96</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-53,64; 3,62</t>
+          <t>-1,55; 6,22</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 4,76</t>
+          <t>-1,56; 4,99</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>3,72; 9,08</t>
+          <t>4,03; 9,48</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 3,13</t>
+          <t>-3,63; 2,68</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,39; 7,16</t>
+          <t>2,5; 6,94</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>6,09; 10,44</t>
+          <t>6,08; 10,3</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-43,6; 1,82</t>
+          <t>-1,33; 3,51</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-24,39%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-0,23%</t>
+          <t>-0,34%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-13,9%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>5,47; 14,07</t>
+          <t>5,27; 13,88</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>8,0; 16,44</t>
+          <t>7,71; 16,05</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-64,46; 4,33</t>
+          <t>-1,78; 7,7</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 5,48</t>
+          <t>-1,74; 5,8</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>4,08; 10,47</t>
+          <t>4,5; 11,05</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 3,62</t>
+          <t>-4,02; 3,1</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,73; 8,52</t>
+          <t>2,85; 8,21</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>6,98; 12,44</t>
+          <t>7,01; 12,26</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-51,25; 2,1</t>
+          <t>-1,54; 4,19</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-11,9</t>
+          <t>-6,1</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-9,75</t>
+          <t>-6,98</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-10,85</t>
+          <t>-6,54</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 0,71</t>
+          <t>-3,8; 0,71</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>9,49; 13,74</t>
+          <t>9,25; 13,44</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-26,27; -6,62</t>
+          <t>-8,36; -3,73</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,15</t>
+          <t>1,0; 5,23</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>10,49; 14,48</t>
+          <t>10,56; 14,63</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-14,6; -7,22</t>
+          <t>-8,99; -4,95</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 2,35</t>
+          <t>-0,68; 2,4</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>10,54; 13,35</t>
+          <t>10,47; 13,41</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-19,12; -7,77</t>
+          <t>-8,32; -4,99</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-16,89%</t>
+          <t>-8,66%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-13,49%</t>
+          <t>-9,65%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-15,2%</t>
+          <t>-9,16%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 1,04</t>
+          <t>-5,29; 1,02</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>13,19; 19,84</t>
+          <t>12,92; 19,52</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-37,49; -9,43</t>
+          <t>-11,67; -5,35</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1,5; 7,2</t>
+          <t>1,37; 7,38</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>14,2; 20,41</t>
+          <t>14,37; 20,64</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-20,15; -10,19</t>
+          <t>-12,3; -6,94</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,3</t>
+          <t>-0,94; 3,39</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>14,59; 18,99</t>
+          <t>14,49; 18,99</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-26,85; -10,96</t>
+          <t>-11,53; -7,05</t>
         </is>
       </c>
     </row>
